--- a/docs/package/05_Delivery/Upload_Templates/Scheme_Vehicle_Lines_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Scheme_Vehicle_Lines_Upload_Template.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Scheme Master &gt; Upload vehicle lines</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Scheme Master &gt; Upload vehicle lines</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
